--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>1265</v>
       </c>
       <c r="Q2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="R2" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="Q4" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="R4" t="n">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="Q5" t="n">
         <v>973</v>
       </c>
       <c r="R5" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q6" t="n">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="R6" t="n">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>1862</v>
       </c>
       <c r="Q7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="R7" t="n">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>헬스보이짐&amp;필라걸 태평점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>healthboygym61@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1380-1662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/w44b3u</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1258</v>
+        <v>1446</v>
       </c>
       <c r="Q9" t="n">
-        <v>1384</v>
+        <v>453</v>
       </c>
       <c r="R9" t="n">
-        <v>2642</v>
+        <v>1899</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1145748404</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1145748404</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>투모어휘트니스 관저3호점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>2more_3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1495-3900</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 서구 관저동로 88 3층 투모어 휘트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://blog.naver.com/2more_3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/w46yuo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>107</v>
+        <v>520</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>167</v>
+        <v>787</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1806931343</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1806931343</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="Q2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R2" t="n">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="Q3" t="n">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="R3" t="n">
-        <v>1365</v>
+        <v>1372</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
+          <t>헬스보이짐&amp;필라걸 둔산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rlaxodid1990@naver.com</t>
+          <t>healthboy_dunsan@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1339-4674</t>
+          <t>0507-1441-8922</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
+          <t>대전 서구 대덕대로 226 명동프라자 2층 헬스보이짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/healthboy_dunsan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ox9bn</t>
+          <t>https://talk.naver.com/ct/w4y2oh</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>603</v>
+        <v>1656</v>
       </c>
       <c r="Q4" t="n">
-        <v>596</v>
+        <v>975</v>
       </c>
       <c r="R4" t="n">
-        <v>1199</v>
+        <v>2631</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1704117576</t>
+          <t>1213678018</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704117576</t>
+          <t>https://m.place.naver.com/place/1213678018</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 둔산점</t>
+          <t>헬스바디필라핏 괴정점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy_dunsan@naver.com</t>
+          <t>healthbody01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1441-8922</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 226 명동프라자 2층 헬스보이짐</t>
+          <t>대전 서구 용문로 41-80 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy_dunsan</t>
+          <t>https://blog.naver.com/healthbody01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4y2oh</t>
+          <t>https://talk.naver.com/ct/w7c7ynn</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,17 +911,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1647</v>
+        <v>179</v>
       </c>
       <c r="Q5" t="n">
-        <v>973</v>
+        <v>765</v>
       </c>
       <c r="R5" t="n">
-        <v>2620</v>
+        <v>944</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1213678018</t>
+          <t>2010388806</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213678018</t>
+          <t>https://m.place.naver.com/place/2010388806</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,34 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더프로짐 둔산 본점</t>
+          <t>헬스보이짐 대전터미널점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>theprogym24@naver.com</t>
+          <t>healthboy65@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1462-2295</t>
+          <t>0507-1323-6569</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 서구 둔지로 13 에이동 7층 701호</t>
+          <t>대전 동구 동서대로 1701 1층, 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_AxeKxgn</t>
+          <t>https://blog.naver.com/healthboy65</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w8vrajk</t>
+          <t>https://talk.naver.com/ct/w4hw66</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>435</v>
+        <v>1148</v>
       </c>
       <c r="Q6" t="n">
-        <v>573</v>
+        <v>1057</v>
       </c>
       <c r="R6" t="n">
-        <v>1008</v>
+        <v>2205</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1506039254</t>
+          <t>1070186913</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506039254</t>
+          <t>https://m.place.naver.com/place/1070186913</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>랩스휘트니스 둔산점 헬스 PT</t>
+          <t>헬스보이짐&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rapsfit17@naver.com</t>
+          <t>healthboy_gwanjeo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1351-2554</t>
+          <t>0507-1494-2153</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 20 대일빌딩 7층</t>
+          <t>대전 서구 관저중로 70 2층 헬스보이짐 &amp; 필라걸</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rapsfit17</t>
+          <t>https://talk.naver.com/ct/w4zxkz?frm=mblog#nafullscreen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tojt</t>
+          <t>https://talk.naver.com/ct/w4zxkz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1862</v>
+        <v>1171</v>
       </c>
       <c r="Q7" t="n">
-        <v>514</v>
+        <v>248</v>
       </c>
       <c r="R7" t="n">
-        <v>2376</v>
+        <v>1419</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1786806222</t>
+          <t>1333673637</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1786806222</t>
+          <t>https://m.place.naver.com/place/1333673637</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스보이짐 대전터미널점</t>
+          <t>더프로짐 둔산 본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>healthboy65@naver.com</t>
+          <t>theprogym24@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1323-6569</t>
+          <t>0507-1462-2295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 동구 동서대로 1701 1층, 2층</t>
+          <t>대전 서구 둔지로 13 에이동 7층 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://forms.gle/P2J7AfuVgNdNCPVv7</t>
+          <t>https://pf.kakao.com/_AxeKxgn</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hw66</t>
+          <t>https://talk.naver.com/ct/w8vrajk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1144</v>
+        <v>438</v>
       </c>
       <c r="Q8" t="n">
-        <v>1056</v>
+        <v>490</v>
       </c>
       <c r="R8" t="n">
-        <v>2200</v>
+        <v>928</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1070186913</t>
+          <t>1506039254</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070186913</t>
+          <t>https://m.place.naver.com/place/1506039254</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 태평점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboygym61@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-1662</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym61</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44b3u</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1446</v>
+        <v>3504</v>
       </c>
       <c r="Q9" t="n">
-        <v>453</v>
+        <v>360</v>
       </c>
       <c r="R9" t="n">
-        <v>1899</v>
+        <v>3864</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1145748404</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145748404</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>투모어휘트니스 관저3호점 헬스 PT</t>
+          <t>다듬체</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2more_3@naver.com</t>
+          <t>hamoneji@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1495-3900</t>
+          <t>042-482-6009</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 88 3층 투모어 휘트니스</t>
+          <t>대전 서구 대덕대로 179 10층 1001호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2more_3</t>
+          <t>https://www.instagram.com/dadeumche.pt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46yuo</t>
+          <t>https://talk.naver.com/ct/wchi4s</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>520</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
-        <v>267</v>
+        <v>624</v>
       </c>
       <c r="R10" t="n">
-        <v>787</v>
+        <v>640</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1806931343</t>
+          <t>21661051</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806931343</t>
+          <t>https://m.place.naver.com/place/21661051</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1510,10 +1506,10 @@
         <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R11" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1532,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="Q4" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="R4" t="n">
-        <v>2631</v>
+        <v>2638</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -918,10 +918,10 @@
         <v>179</v>
       </c>
       <c r="Q5" t="n">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="R5" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 대전터미널점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy65@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1323-6569</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 동구 동서대로 1701 1층, 2층</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy65</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hw66</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1148</v>
+        <v>3509</v>
       </c>
       <c r="Q6" t="n">
-        <v>1057</v>
+        <v>360</v>
       </c>
       <c r="R6" t="n">
-        <v>2205</v>
+        <v>3869</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1070186913</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070186913</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라테스 관저점</t>
+          <t>헬스보이짐 대전터미널점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy_gwanjeo@naver.com</t>
+          <t>healthboy65@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1494-2153</t>
+          <t>0507-1323-6569</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 서구 관저중로 70 2층 헬스보이짐 &amp; 필라걸</t>
+          <t>대전 동구 동서대로 1701 1층, 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zxkz?frm=mblog#nafullscreen</t>
+          <t>https://blog.naver.com/healthboy65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zxkz</t>
+          <t>https://talk.naver.com/ct/w4hw66</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1171</v>
+        <v>1148</v>
       </c>
       <c r="Q7" t="n">
-        <v>248</v>
+        <v>1057</v>
       </c>
       <c r="R7" t="n">
-        <v>1419</v>
+        <v>2205</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,56 +1126,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1333673637</t>
+          <t>1070186913</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333673637</t>
+          <t>https://m.place.naver.com/place/1070186913</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더프로짐 둔산 본점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>theprogym24@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1462-2295</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 서구 둔지로 13 에이동 7층 701호</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_AxeKxgn</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w8vrajk</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>438</v>
+        <v>1255</v>
       </c>
       <c r="Q8" t="n">
-        <v>490</v>
+        <v>1395</v>
       </c>
       <c r="R8" t="n">
-        <v>928</v>
+        <v>2650</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1506039254</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506039254</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>rlaxodid1990@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1339-4674</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/w4ox9bn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3504</v>
+        <v>656</v>
       </c>
       <c r="Q9" t="n">
-        <v>360</v>
+        <v>616</v>
       </c>
       <c r="R9" t="n">
-        <v>3864</v>
+        <v>1272</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>1704117576</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/1704117576</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>다듬체</t>
+          <t>짐포스 둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hamoneji@naver.com</t>
+          <t>gymforxe@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>042-482-6009</t>
+          <t>0507-1487-4453</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 179 10층 1001호</t>
+          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dadeumche.pt</t>
+          <t>https://blog.naver.com/gymforxe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wchi4s</t>
+          <t>https://talk.naver.com/ct/w5wswx</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>1966</v>
       </c>
       <c r="Q10" t="n">
-        <v>624</v>
+        <v>126</v>
       </c>
       <c r="R10" t="n">
-        <v>640</v>
+        <v>2092</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>21661051</t>
+          <t>1928169003</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21661051</t>
+          <t>https://m.place.naver.com/place/1928169003</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>헬스보이짐&amp;필라걸 태평점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>healthboygym61@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>0507-1380-1662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
+          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jupilates11</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
+          <t>https://talk.naver.com/ct/w44b3u</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>116</v>
+        <v>1448</v>
       </c>
       <c r="Q11" t="n">
-        <v>339</v>
+        <v>455</v>
       </c>
       <c r="R11" t="n">
-        <v>455</v>
+        <v>1903</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1518,209 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1618277867</t>
+          <t>1145748404</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
+          <t>https://m.place.naver.com/place/1145748404</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>랩스휘트니스 유성온천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rapsfit614@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1477-2553</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rapsfit614</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>4468</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1078</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5546</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1186158075</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1186158075</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IAME PT&amp;필라테스 관저점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>iame_center@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>042-488-7021</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/iame_center</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>169</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>16151158</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16151158</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1143,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>rlaxodid1990@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1339-4674</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/w4ox9bn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1255</v>
+        <v>656</v>
       </c>
       <c r="Q8" t="n">
-        <v>1395</v>
+        <v>615</v>
       </c>
       <c r="R8" t="n">
-        <v>2650</v>
+        <v>1271</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1704117576</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1704117576</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
+          <t>짐포스 둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rlaxodid1990@naver.com</t>
+          <t>gymforxe@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1339-4674</t>
+          <t>0507-1487-4453</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
+          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/gymforxe</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ox9bn</t>
+          <t>https://talk.naver.com/ct/w5wswx</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>656</v>
+        <v>1966</v>
       </c>
       <c r="Q9" t="n">
-        <v>616</v>
+        <v>126</v>
       </c>
       <c r="R9" t="n">
-        <v>1272</v>
+        <v>2092</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1704117576</t>
+          <t>1928169003</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704117576</t>
+          <t>https://m.place.naver.com/place/1928169003</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐포스 둔산점 헬스 PT</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymforxe@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-4453</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wswx</t>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1966</v>
+        <v>4468</v>
       </c>
       <c r="Q10" t="n">
-        <v>126</v>
+        <v>1078</v>
       </c>
       <c r="R10" t="n">
-        <v>2092</v>
+        <v>5546</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1928169003</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928169003</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 태평점</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthboygym61@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1380-1662</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym61</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44b3u</t>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1448</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>455</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>1903</v>
+        <v>169</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,207 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1145748404</t>
+          <t>16151158</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145748404</t>
+          <t>https://m.place.naver.com/place/16151158</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>랩스휘트니스 유성온천점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rapsfit614@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1477-2553</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/rapsfit614</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>4468</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1078</v>
-      </c>
-      <c r="R12" t="n">
-        <v>5546</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1186158075</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>iame_center@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>042-488-7021</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/iame_center</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>62</v>
-      </c>
-      <c r="R13" t="n">
-        <v>169</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>16151158</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/16151158</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1266</v>
+        <v>1255</v>
       </c>
       <c r="Q2" t="n">
-        <v>203</v>
+        <v>1395</v>
       </c>
       <c r="R2" t="n">
-        <v>1469</v>
+        <v>2650</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포레스핏 갈마점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4lessfit@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1470-0223</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 164 8층</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/4lessfit_galma</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4az0w</t>
+          <t>https://talk.naver.com/ct/wuudbce</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>694</v>
+        <v>1266</v>
       </c>
       <c r="Q3" t="n">
-        <v>678</v>
+        <v>203</v>
       </c>
       <c r="R3" t="n">
-        <v>1372</v>
+        <v>1469</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1636638315</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636638315</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>헬스보이짐 테크노밸리점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>healthboy48@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1345-9430</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 유성구 테크노중앙로 54 8층 헬스보이짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://blog.naver.com/healthboy48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/w48rq5</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3509</v>
+        <v>2816</v>
       </c>
       <c r="Q6" t="n">
-        <v>360</v>
+        <v>733</v>
       </c>
       <c r="R6" t="n">
-        <v>3869</v>
+        <v>3549</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>1989793562</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/1989793562</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 대전터미널점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboy65@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1323-6569</t>
+          <t>0507-1307-9497</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 동구 동서대로 1701 1층, 2층</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy65</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hw66</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1148</v>
+        <v>3509</v>
       </c>
       <c r="Q7" t="n">
-        <v>1057</v>
+        <v>360</v>
       </c>
       <c r="R7" t="n">
-        <v>2205</v>
+        <v>3869</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1070186913</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070186913</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4468</v>
+        <v>4469</v>
       </c>
       <c r="Q10" t="n">
         <v>1078</v>
       </c>
       <c r="R10" t="n">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/wuudbce</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1255</v>
+        <v>1268</v>
       </c>
       <c r="Q2" t="n">
-        <v>1395</v>
+        <v>203</v>
       </c>
       <c r="R2" t="n">
-        <v>2650</v>
+        <v>1471</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>포레스핏 갈마점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>4lessfit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1470-0223</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 서구 대덕대로 164 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://www.instagram.com/4lessfit_galma</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/w4az0w</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1266</v>
+        <v>694</v>
       </c>
       <c r="Q3" t="n">
-        <v>203</v>
+        <v>679</v>
       </c>
       <c r="R3" t="n">
-        <v>1469</v>
+        <v>1373</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1636638315</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1636638315</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="Q4" t="n">
         <v>980</v>
       </c>
       <c r="R4" t="n">
-        <v>2638</v>
+        <v>2640</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q5" t="n">
         <v>769</v>
       </c>
       <c r="R5" t="n">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="Q6" t="n">
         <v>733</v>
       </c>
       <c r="R6" t="n">
-        <v>3549</v>
+        <v>3551</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3509</v>
+        <v>3511</v>
       </c>
       <c r="Q7" t="n">
         <v>360</v>
       </c>
       <c r="R7" t="n">
-        <v>3869</v>
+        <v>3871</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
         <v>656</v>
       </c>
       <c r="Q8" t="n">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="R8" t="n">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐포스 둔산점 헬스 PT</t>
+          <t>헬스보이짐&amp;필라걸 태평점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymforxe@naver.com</t>
+          <t>healthboygym61@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-4453</t>
+          <t>0507-1380-1662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
+          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wswx</t>
+          <t>https://talk.naver.com/ct/w44b3u</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1966</v>
+        <v>1448</v>
       </c>
       <c r="Q9" t="n">
-        <v>126</v>
+        <v>455</v>
       </c>
       <c r="R9" t="n">
-        <v>2092</v>
+        <v>1903</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1928169003</t>
+          <t>1145748404</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928169003</t>
+          <t>https://m.place.naver.com/place/1145748404</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1408,10 +1408,10 @@
         <v>4469</v>
       </c>
       <c r="Q10" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="R10" t="n">
-        <v>5547</v>
+        <v>5548</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>주 필라테스&amp;요가 관평점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>jugwpy7755@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1399-7758</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="R11" t="n">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1618277867</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1268</v>
+        <v>1255</v>
       </c>
       <c r="Q2" t="n">
-        <v>203</v>
+        <v>1395</v>
       </c>
       <c r="R2" t="n">
-        <v>1471</v>
+        <v>2650</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포레스핏 갈마점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4lessfit@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1470-0223</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 164 8층</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/4lessfit_galma</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4az0w</t>
+          <t>https://talk.naver.com/ct/wuudbce</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>694</v>
+        <v>1268</v>
       </c>
       <c r="Q3" t="n">
-        <v>679</v>
+        <v>203</v>
       </c>
       <c r="R3" t="n">
-        <v>1373</v>
+        <v>1471</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1636638315</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636638315</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy_dunsan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthbody01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy48</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>01edpaik@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym61</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1430,105 +1430,203 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>62</v>
+      </c>
+      <c r="R11" t="n">
+        <v>169</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>16151158</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16151158</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>주 필라테스&amp;요가 관평점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jugwpy7755@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1399-7758</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jupilates11</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>116</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>339</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>455</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1618277867</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboy_dunsan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="Q4" t="n">
         <v>980</v>
       </c>
       <c r="R4" t="n">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthbody01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -918,10 +918,10 @@
         <v>177</v>
       </c>
       <c r="Q5" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="R5" t="n">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboy48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01edpaik@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4469</v>
+        <v>4470</v>
       </c>
       <c r="Q10" t="n">
         <v>1079</v>
       </c>
       <c r="R10" t="n">
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/wuudbce</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="Q2" t="n">
-        <v>1395</v>
+        <v>204</v>
       </c>
       <c r="R2" t="n">
-        <v>2650</v>
+        <v>1473</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>모던 휘트니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>mr2416_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1375-2416</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 중구 목중로 22 2층,3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://blog.naver.com/mr2416_</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/wqu7g29</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1268</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="n">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="R3" t="n">
-        <v>1471</v>
+        <v>242</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1966964430</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1966964430</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="Q4" t="n">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="R4" t="n">
-        <v>2641</v>
+        <v>2644</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>177</v>
       </c>
       <c r="Q5" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R5" t="n">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -952,34 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 테크노밸리점</t>
+          <t>헬스보이짐&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy48@naver.com</t>
+          <t>healthboy_gwanjeo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1345-9430</t>
+          <t>0507-1494-2153</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 유성구 테크노중앙로 54 8층 헬스보이짐</t>
+          <t>대전 서구 관저중로 70 2층 헬스보이짐 &amp; 필라걸</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy48</t>
+          <t>https://talk.naver.com/ct/w4zxkz?frm=mblog#nafullscreen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48rq5</t>
+          <t>https://talk.naver.com/ct/w4zxkz</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2818</v>
+        <v>1178</v>
       </c>
       <c r="Q6" t="n">
-        <v>733</v>
+        <v>248</v>
       </c>
       <c r="R6" t="n">
-        <v>3551</v>
+        <v>1426</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1989793562</t>
+          <t>1333673637</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989793562</t>
+          <t>https://m.place.naver.com/place/1333673637</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 태평점</t>
+          <t>짐포스 둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboygym61@naver.com</t>
+          <t>gymforxe@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-1662</t>
+          <t>0507-1487-4453</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
+          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym61</t>
+          <t>https://blog.naver.com/gymforxe</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44b3u</t>
+          <t>https://talk.naver.com/ct/w5wswx</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1448</v>
+        <v>1966</v>
       </c>
       <c r="Q9" t="n">
-        <v>455</v>
+        <v>126</v>
       </c>
       <c r="R9" t="n">
-        <v>1903</v>
+        <v>2092</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1145748404</t>
+          <t>1928169003</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145748404</t>
+          <t>https://m.place.naver.com/place/1928169003</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
+          <t>주 필라테스&amp;요가 관평점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>iame_center@naver.com</t>
+          <t>jugwpy7755@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7023</t>
+          <t>0507-1399-7758</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
+          <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iame_center</t>
+          <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
+          <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="R11" t="n">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16151158</t>
+          <t>1618277867</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16151158</t>
+          <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>주 필라테스&amp;요가 관평점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jugwpy7755@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1399-7758</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jupilates11</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>116</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>339</v>
-      </c>
-      <c r="R12" t="n">
-        <v>455</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1618277867</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모던 휘트니스</t>
+          <t>포레스핏 갈마점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mr2416_@naver.com</t>
+          <t>4lessfit@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-2416</t>
+          <t>0507-1470-0223</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 중구 목중로 22 2층,3층</t>
+          <t>대전 서구 대덕대로 164 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mr2416_</t>
+          <t>https://www.instagram.com/4lessfit_galma</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqu7g29</t>
+          <t>https://talk.naver.com/ct/w4az0w</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>61</v>
+        <v>694</v>
       </c>
       <c r="Q3" t="n">
-        <v>181</v>
+        <v>679</v>
       </c>
       <c r="R3" t="n">
-        <v>242</v>
+        <v>1373</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1966964430</t>
+          <t>1636638315</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966964430</t>
+          <t>https://m.place.naver.com/place/1636638315</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="Q4" t="n">
         <v>981</v>
       </c>
       <c r="R4" t="n">
-        <v>2644</v>
+        <v>2646</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q8" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="R8" t="n">
         <v>1274</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="Q9" t="n">
         <v>126</v>
       </c>
       <c r="R9" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4470</v>
+        <v>4469</v>
       </c>
       <c r="Q10" t="n">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="R10" t="n">
         <v>5549</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="Q2" t="n">
         <v>204</v>
       </c>
       <c r="R2" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>1665</v>
       </c>
       <c r="Q4" t="n">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="R4" t="n">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -858,25 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스바디필라핏 괴정점</t>
+          <t>짐포스 갈마둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthbody01@naver.com</t>
+          <t>gymforxe_2nd@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1307-9497</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 서구 용문로 41-80 2층</t>
+          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthbody01</t>
+          <t>https://blog.naver.com/gymforxe_2nd</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7c7ynn</t>
+          <t>https://talk.naver.com/ct/wccep6d</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,17 +915,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>177</v>
+        <v>3513</v>
       </c>
       <c r="Q5" t="n">
-        <v>771</v>
+        <v>360</v>
       </c>
       <c r="R5" t="n">
-        <v>948</v>
+        <v>3873</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2010388806</t>
+          <t>1868031100</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010388806</t>
+          <t>https://m.place.naver.com/place/1868031100</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라테스 관저점</t>
+          <t>바디스타 휘트니스 용문가장점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboy_gwanjeo@naver.com</t>
+          <t>bodystarfit@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1494-2153</t>
+          <t>0507-1327-6652</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전 서구 관저중로 70 2층 헬스보이짐 &amp; 필라걸</t>
+          <t>대전 서구 도산로 330 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zxkz?frm=mblog#nafullscreen</t>
+          <t>https://blog.naver.com/bodystarfit</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4zxkz</t>
+          <t>https://talk.naver.com/ct/w40f10</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1178</v>
+        <v>2259</v>
       </c>
       <c r="Q6" t="n">
-        <v>248</v>
+        <v>542</v>
       </c>
       <c r="R6" t="n">
-        <v>1426</v>
+        <v>2801</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1333673637</t>
+          <t>1674043008</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333673637</t>
+          <t>https://m.place.naver.com/place/1674043008</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐포스 갈마둔산점 헬스 PT</t>
+          <t>헬스보이짐&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymforxe_2nd@naver.com</t>
+          <t>healthboy_gwanjeo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1307-9497</t>
+          <t>0507-1494-2153</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로 4 5층 짐포스 갈마둔산점</t>
+          <t>대전 서구 관저중로 70 2층 헬스보이짐 &amp; 필라걸</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe_2nd</t>
+          <t>https://talk.naver.com/ct/w4zxkz?frm=mblog#nafullscreen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wccep6d</t>
+          <t>https://talk.naver.com/ct/w4zxkz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3511</v>
+        <v>1178</v>
       </c>
       <c r="Q7" t="n">
-        <v>360</v>
+        <v>248</v>
       </c>
       <c r="R7" t="n">
-        <v>3871</v>
+        <v>1426</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1868031100</t>
+          <t>1333673637</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868031100</t>
+          <t>https://m.place.naver.com/place/1333673637</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1212,10 +1216,10 @@
         <v>655</v>
       </c>
       <c r="Q8" t="n">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="R8" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="Q9" t="n">
         <v>126</v>
       </c>
       <c r="R9" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1339,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>헬스보이짐&amp;필라걸 태평점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>healthboygym61@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1380-1662</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
+          <t>https://talk.naver.com/ct/w44b3u</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4469</v>
+        <v>1453</v>
       </c>
       <c r="Q10" t="n">
-        <v>1080</v>
+        <v>455</v>
       </c>
       <c r="R10" t="n">
-        <v>5549</v>
+        <v>1908</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>1145748404</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/1145748404</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,96 +1441,292 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주 필라테스&amp;요가 관평점</t>
+          <t>투모어휘트니스 관저3호점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jugwpy7755@naver.com</t>
+          <t>2more_3@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-7758</t>
+          <t>0507-1495-3900</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>대전 서구 관저동로 88 3층 투모어 휘트니스</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/2more_3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46yuo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>519</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>271</v>
+      </c>
+      <c r="R11" t="n">
+        <v>790</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1806931343</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806931343</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>랩스휘트니스 유성온천점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rapsfit614@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1477-2553</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rapsfit614</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>4469</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5549</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1186158075</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1186158075</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>주 필라테스&amp;요가 관평점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jugwpy7755@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1399-7758</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>대전 유성구 관평2로 48 올리브영 2층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://www.instagram.com/jupilates11</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w449lr</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>116</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>339</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>455</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1618277867</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1618277867</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="Q4" t="n">
         <v>980</v>
       </c>
       <c r="R4" t="n">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,41 +1140,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rlaxodid1990@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1339-4674</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ox9bn</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>655</v>
+        <v>1256</v>
       </c>
       <c r="Q8" t="n">
-        <v>621</v>
+        <v>1395</v>
       </c>
       <c r="R8" t="n">
-        <v>1276</v>
+        <v>2651</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1704117576</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704117576</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐포스 둔산점 헬스 PT</t>
+          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymforxe@naver.com</t>
+          <t>rlaxodid1990@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-4453</t>
+          <t>0507-1339-4674</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
+          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe</t>
+          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wswx</t>
+          <t>https://talk.naver.com/ct/w4ox9bn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1968</v>
+        <v>659</v>
       </c>
       <c r="Q9" t="n">
-        <v>126</v>
+        <v>621</v>
       </c>
       <c r="R9" t="n">
-        <v>2094</v>
+        <v>1280</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1928169003</t>
+          <t>1704117576</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928169003</t>
+          <t>https://m.place.naver.com/place/1704117576</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 태평점</t>
+          <t>짐포스 둔산점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>healthboygym61@naver.com</t>
+          <t>gymforxe@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1380-1662</t>
+          <t>0507-1487-4453</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
+          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym61</t>
+          <t>https://blog.naver.com/gymforxe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44b3u</t>
+          <t>https://talk.naver.com/ct/w5wswx</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1453</v>
+        <v>1968</v>
       </c>
       <c r="Q10" t="n">
-        <v>455</v>
+        <v>126</v>
       </c>
       <c r="R10" t="n">
-        <v>1908</v>
+        <v>2094</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1145748404</t>
+          <t>1928169003</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145748404</t>
+          <t>https://m.place.naver.com/place/1928169003</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>투모어휘트니스 관저3호점 헬스 PT</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2more_3@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1495-3900</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 관저동로 88 3층 투모어 휘트니스</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/2more_3</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46yuo</t>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>519</v>
+        <v>4469</v>
       </c>
       <c r="Q11" t="n">
-        <v>271</v>
+        <v>1080</v>
       </c>
       <c r="R11" t="n">
-        <v>790</v>
+        <v>5549</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1806931343</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806931343</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1544,29 +1544,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>4469</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="n">
-        <v>1080</v>
+        <v>62</v>
       </c>
       <c r="R12" t="n">
-        <v>5549</v>
+        <v>169</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,115 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>16151158</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/16151158</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>주 필라테스&amp;요가 관평점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>jugwpy7755@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1399-7758</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대전 유성구 관평2로 48 올리브영 2층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jupilates11</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w449lr</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>116</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>339</v>
-      </c>
-      <c r="R13" t="n">
-        <v>455</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1618277867</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1618277867</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대전_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대전_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>팀메이크짐 헬스 PT 대전역점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>meal10049@naver.com</t>
+          <t>resort_7@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1349-6862</t>
+          <t>0507-1330-2427</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
+          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/meal10049</t>
+          <t>https://blog.naver.com/resort_7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuudbce</t>
+          <t>https://talk.naver.com/ct/w4kl17</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1270</v>
+        <v>1256</v>
       </c>
       <c r="Q2" t="n">
-        <v>204</v>
+        <v>1395</v>
       </c>
       <c r="R2" t="n">
-        <v>1474</v>
+        <v>2651</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1576974587</t>
+          <t>1882767853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1576974587</t>
+          <t>https://m.place.naver.com/place/1882767853</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포레스핏 갈마점</t>
+          <t>팀메이크짐 헬스 PT 대전역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4lessfit@naver.com</t>
+          <t>meal10049@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1470-0223</t>
+          <t>0507-1349-6862</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 164 8층</t>
+          <t>대전 동구 동대전로46번길 7 5층 팀메이크</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/4lessfit_galma</t>
+          <t>https://blog.naver.com/meal10049</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4az0w</t>
+          <t>https://talk.naver.com/ct/wuudbce</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>694</v>
+        <v>1270</v>
       </c>
       <c r="Q3" t="n">
-        <v>679</v>
+        <v>204</v>
       </c>
       <c r="R3" t="n">
-        <v>1373</v>
+        <v>1474</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1636638315</t>
+          <t>1576974587</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636638315</t>
+          <t>https://m.place.naver.com/place/1576974587</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1147,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 대전점</t>
+          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>resort_7@naver.com</t>
+          <t>rlaxodid1990@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-2427</t>
+          <t>0507-1339-4674</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전 서구 계룡로 598 롯데백화점 4층</t>
+          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_7</t>
+          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kl17</t>
+          <t>https://talk.naver.com/ct/w4ox9bn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1256</v>
+        <v>659</v>
       </c>
       <c r="Q8" t="n">
-        <v>1395</v>
+        <v>621</v>
       </c>
       <c r="R8" t="n">
-        <v>2651</v>
+        <v>1280</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1882767853</t>
+          <t>1704117576</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882767853</t>
+          <t>https://m.place.naver.com/place/1704117576</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아레나휘트니스&amp;레나필라테스 유성점</t>
+          <t>헬스보이짐&amp;필라걸 태평점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rlaxodid1990@naver.com</t>
+          <t>healthboygym61@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1339-4674</t>
+          <t>0507-1380-1662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전 유성구 대학로 86 포커스타운 8층 아레나휘트니스</t>
+          <t>대전 중구 태평로 83 5층 북동쪽호 헬스보이짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arena_yuseong?igsh=YnY0YzQ0bWRra2Ex&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/healthboygym61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ox9bn</t>
+          <t>https://talk.naver.com/ct/w44b3u</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>659</v>
+        <v>1453</v>
       </c>
       <c r="Q9" t="n">
-        <v>621</v>
+        <v>455</v>
       </c>
       <c r="R9" t="n">
-        <v>1280</v>
+        <v>1908</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1704117576</t>
+          <t>1145748404</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704117576</t>
+          <t>https://m.place.naver.com/place/1145748404</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐포스 둔산점 헬스 PT</t>
+          <t>랩스휘트니스 유성온천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymforxe@naver.com</t>
+          <t>rapsfit614@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-4453</t>
+          <t>0507-1477-2553</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 대덕대로 222 강남프라자 4층</t>
+          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymforxe</t>
+          <t>https://blog.naver.com/rapsfit614</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wswx</t>
+          <t>https://talk.naver.com/ct/w4fdl1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1968</v>
+        <v>4470</v>
       </c>
       <c r="Q10" t="n">
-        <v>126</v>
+        <v>1080</v>
       </c>
       <c r="R10" t="n">
-        <v>2094</v>
+        <v>5550</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1928169003</t>
+          <t>1186158075</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928169003</t>
+          <t>https://m.place.naver.com/place/1186158075</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>랩스휘트니스 유성온천점</t>
+          <t>IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rapsfit614@naver.com</t>
+          <t>iame_center@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1477-2553</t>
+          <t>0507-1360-7023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 유성구 계룡로52번길 11 세움펠리피아 주상복합아파트 2층 201~205호</t>
+          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rapsfit614</t>
+          <t>https://blog.naver.com/iame_center</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fdl1</t>
+          <t>https://talk.naver.com/ct/wbev6vs</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4469</v>
+        <v>107</v>
       </c>
       <c r="Q11" t="n">
-        <v>1080</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>5549</v>
+        <v>169</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1522,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1186158075</t>
+          <t>16151158</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1186158075</t>
+          <t>https://m.place.naver.com/place/16151158</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IAME PT&amp;필라테스 관저점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>iame_center@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1360-7023</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대전 서구 관저동로 162 6층 IAME PT&amp;필라테스 관저점</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/iame_center</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wbev6vs</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>62</v>
-      </c>
-      <c r="R12" t="n">
-        <v>169</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>16151158</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/16151158</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
